--- a/3/РБП/Шаблон_SWOT-анализ.xlsx
+++ b/3/РБП/Шаблон_SWOT-анализ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\MIREA\3\РБП\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01BDAB7-30CD-4496-BF28-E9F0FD557FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94E2419-A2A5-44F1-9E4D-8E0D77337CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Сильные стороны
 (Strengths)</t>
@@ -99,12 +99,6 @@
     <t>Автоматизация подбора конфигураций (конфигуратор)</t>
   </si>
   <si>
-    <t>Развитие собственного бренда и узнаваемости</t>
-  </si>
-  <si>
-    <t>Внедрение аналитики и динамического ценообразования</t>
-  </si>
-  <si>
     <t>Расширение ассортимента (готовые решения под ниши)</t>
   </si>
   <si>
@@ -130,6 +124,15 @@
   </si>
   <si>
     <t>Оптимизация карточек товаров (SEO, описание)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Разработка и использование собственной CMS-системы</t>
+  </si>
+  <si>
+    <t>Производство собственных брендовых комплектующих</t>
   </si>
 </sst>
 </file>
@@ -621,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="70" bestFit="1" customWidth="1"/>
@@ -711,10 +714,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -722,31 +725,31 @@
         <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -754,14 +757,19 @@
         <v>17</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B16" s="11"/>
+    </row>
+    <row r="21" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
